--- a/artfynd/A 59538-2024 artfynd.xlsx
+++ b/artfynd/A 59538-2024 artfynd.xlsx
@@ -675,37 +675,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133420782</v>
+        <v>133420798</v>
       </c>
       <c r="B2" t="n">
-        <v>56832</v>
+        <v>56816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -753,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>registreringar under 24 nätter</t>
+          <t>registreringar under 4 nätter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,33 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133420798</v>
+        <v>133420782</v>
       </c>
       <c r="B3" t="n">
-        <v>56816</v>
+        <v>56832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -864,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>registreringar under 4 nätter</t>
+          <t>registreringar under 24 nätter</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 59538-2024 artfynd.xlsx
+++ b/artfynd/A 59538-2024 artfynd.xlsx
@@ -675,33 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133420798</v>
+        <v>133420782</v>
       </c>
       <c r="B2" t="n">
-        <v>56816</v>
+        <v>56832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -749,17 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>registreringar under 4 nätter</t>
+          <t>registreringar under 24 nätter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +790,33 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133420782</v>
+        <v>133420798</v>
       </c>
       <c r="B3" t="n">
-        <v>56832</v>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -864,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>registreringar under 24 nätter</t>
+          <t>registreringar under 4 nätter</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 59538-2024 artfynd.xlsx
+++ b/artfynd/A 59538-2024 artfynd.xlsx
@@ -790,33 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133420798</v>
+        <v>133420812</v>
       </c>
       <c r="B3" t="n">
-        <v>56833</v>
+        <v>56852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -874,7 +878,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>registreringar under 4 nätter</t>
+          <t>registrering under 4 nätter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133420810</v>
+        <v>133420770</v>
       </c>
       <c r="B5" t="n">
         <v>56854</v>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1094,17 +1098,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>registreringar under 4 nätter</t>
+          <t>registreringar under 24 nätter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,37 +1135,33 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133420812</v>
+        <v>133420756</v>
       </c>
       <c r="B6" t="n">
-        <v>56852</v>
+        <v>56833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1209,17 +1209,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>registrering under 4 nätter</t>
+          <t>registreringar under 24 nätter</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 59538-2024 artfynd.xlsx
+++ b/artfynd/A 59538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420782</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420812</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420761</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,8 +1268,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420756</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>